--- a/data/gc-stem_d2l_courses.xlsx
+++ b/data/gc-stem_d2l_courses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\automation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E446016-D62E-4052-9F4A-F49F207C173D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D030D255-F465-438A-A707-8CF68DD0902B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5463728D-3FB0-4F48-833B-CBEF51173160}"/>
   </bookViews>
@@ -39,14 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="392">
   <si>
     <t>Program</t>
   </si>
   <si>
-    <t>OrgUnitID</t>
-  </si>
-  <si>
     <t>Semester</t>
   </si>
   <si>
@@ -663,13 +660,568 @@
   </si>
   <si>
     <t>CourseURL</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483817</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483543</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483507</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483508</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483509</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483510</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483511</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483512</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483513</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483514</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483515</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483516</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483517</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483518</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483519</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483520</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483521</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483522</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483523</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483524</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483525</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483526</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483527</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483528</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483529</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483530</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483531</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483532</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483533</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483534</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483535</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483536</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483537</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483538</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483539</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483540</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483541</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483544</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483545</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483546</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483547</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483548</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483549</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483550</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483551</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483552</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483553</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483554</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483555</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483556</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483557</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483558</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483641</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483642</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483643</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483644</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483645</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483646</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483647</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2441925</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483648</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2374297</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2441926</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2374299</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483649</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483650</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483651</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483652</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483815</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483818</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483819</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483820</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483821</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483822</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483823</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483824</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483825</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483826</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483827</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483828</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483829</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483830</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483831</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483832</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483833</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483834</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483835</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483836</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483837</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483838</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483839</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483840</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483841</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483842</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483843</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483844</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483845</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483846</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483847</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483848</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483849</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483850</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483851</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483852</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483853</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483854</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483855</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483856</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483857</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483858</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483859</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483888</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483889</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483890</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483891</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483892</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483893</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483894</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483895</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483896</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483897</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483898</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483899</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483900</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483901</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483902</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483903</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483904</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483905</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483906</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483907</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483908</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483909</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483910</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483911</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483912</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483913</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483914</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483406</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483407</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483408</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483409</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483410</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483411</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483412</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483413</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483434</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483435</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483589</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483590</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483591</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483592</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483593</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483594</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483595</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483596</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483655</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483656</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483657</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483658</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484016</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484017</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484018</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484019</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484020</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484021</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484022</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484113</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484114</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484115</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484116</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484117</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484118</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484119</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484120</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484121</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484122</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484123</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484124</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484125</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484126</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484127</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484128</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2484129</t>
+  </si>
+  <si>
+    <t>https://learn.snhu.edu/d2l/p/home/2483542</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -722,6 +1274,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202122"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -744,7 +1309,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -772,7 +1337,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1108,4517 +1676,5069 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AC3F99-AD61-4E20-9147-57E3EA57EF48}">
-  <dimension ref="A1:I187"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
-    <col min="2" max="2" width="10.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+      <c r="B1" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>203</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>3</v>
+        <v>204</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="I1" s="11" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D16" s="6" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H16" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H17" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H18" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>25</v>
+        <v>3</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>26</v>
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H20" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H21" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>28</v>
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H22" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>29</v>
+        <v>3</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H23" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>30</v>
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H24" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>31</v>
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H25" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>32</v>
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H26" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>34</v>
+      <c r="C27" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H27" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H28" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H29" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H30" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H31" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H33" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H34" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H35" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H36" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H37" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H38" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>32</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H39" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>48</v>
+      <c r="C40" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H40" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H41" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H42" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H43" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H44" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H45" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H46" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H47" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H48" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H49" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H50" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H51" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>60</v>
+        <v>46</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H52" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H53" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>62</v>
+        <v>46</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H54" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>64</v>
+      <c r="C55" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H55" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H56" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H56" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H57" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H58" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H59" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H60" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H61" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H62" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H64" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>74</v>
+        <v>62</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H65" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>75</v>
+        <v>62</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H66" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>76</v>
+        <v>62</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H67" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>77</v>
+        <v>62</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H68" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>78</v>
+        <v>62</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H69" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>79</v>
+        <v>62</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H70" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>81</v>
+      <c r="C71" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H71" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H72" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H73" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H74" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H75" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H76" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H77" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>88</v>
+        <v>79</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H78" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>89</v>
+        <v>79</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H79" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>90</v>
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H80" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>91</v>
+        <v>79</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H81" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>92</v>
+        <v>79</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H82" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H83" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>94</v>
+        <v>79</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H84" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H84" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>95</v>
+        <v>79</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H85" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>96</v>
+        <v>79</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H86" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H86" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>97</v>
+        <v>79</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F87" s="6" t="s">
+      <c r="F87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H87" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>98</v>
+        <v>79</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H88" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H88" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>99</v>
+        <v>79</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F89" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H89" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>100</v>
+        <v>79</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F90" s="6" t="s">
+      <c r="F90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H90" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>101</v>
+        <v>79</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F91" s="6" t="s">
+      <c r="F91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H91" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>102</v>
+        <v>79</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F92" s="6" t="s">
+      <c r="F92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H92" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>103</v>
+        <v>79</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H93" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H93" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>104</v>
+        <v>79</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>104</v>
+        <v>5</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F94" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H94" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>105</v>
+        <v>79</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F95" s="6" t="s">
+      <c r="F95" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H95" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>106</v>
+        <v>79</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F96" s="6" t="s">
+      <c r="F96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H96" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>107</v>
+        <v>79</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F97" s="6" t="s">
+      <c r="F97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H97" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>108</v>
+        <v>79</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>108</v>
+        <v>5</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F98" s="6" t="s">
+      <c r="F98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H98" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>109</v>
+        <v>79</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F99" s="6" t="s">
+      <c r="F99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H99" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>110</v>
+        <v>79</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F100" s="6" t="s">
+      <c r="F100" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H100" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>111</v>
+        <v>79</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F101" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H101" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>112</v>
+        <v>79</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F102" s="6" t="s">
+      <c r="F102" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H102" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>113</v>
+        <v>79</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F103" s="6" t="s">
+      <c r="F103" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H103" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>114</v>
+        <v>79</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>114</v>
+        <v>5</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F104" s="6" t="s">
+      <c r="F104" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H104" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>115</v>
+        <v>79</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F105" s="6" t="s">
+      <c r="F105" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H105" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>116</v>
+        <v>79</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F106" s="6" t="s">
+      <c r="F106" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H106" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>117</v>
+        <v>79</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F107" s="6" t="s">
+      <c r="F107" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H107" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>118</v>
+        <v>79</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F108" s="6" t="s">
+      <c r="F108" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H108" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>119</v>
+        <v>79</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F109" s="6" t="s">
+      <c r="F109" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H109" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H109" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>120</v>
+        <v>79</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F110" s="6" t="s">
+      <c r="F110" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H110" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H110" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>121</v>
+        <v>79</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F111" s="6" t="s">
+      <c r="F111" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H111" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>122</v>
+        <v>79</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F112" s="6" t="s">
+      <c r="F112" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H112" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H112" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>123</v>
+        <v>79</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="F113" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H113" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>125</v>
+      <c r="C114" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F114" s="6" t="s">
+      <c r="F114" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H114" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F115" s="6" t="s">
+      <c r="F115" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H115" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F116" s="6" t="s">
+      <c r="F116" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H116" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>128</v>
+        <v>5</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F117" s="6" t="s">
+      <c r="F117" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H117" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H117" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>129</v>
+        <v>123</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F118" s="6" t="s">
+      <c r="F118" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F119" s="6" t="s">
+      <c r="F119" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H119" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F120" s="6" t="s">
+      <c r="F120" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H120" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>132</v>
+        <v>123</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F121" s="6" t="s">
+      <c r="F121" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H121" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>133</v>
+        <v>123</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F122" s="6" t="s">
+      <c r="F122" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H122" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>134</v>
+        <v>123</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>134</v>
+        <v>5</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="F123" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H123" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>135</v>
+        <v>123</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>135</v>
+        <v>5</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="F124" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H124" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>136</v>
+        <v>123</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>136</v>
+        <v>5</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F125" s="6" t="s">
+      <c r="F125" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H125" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>137</v>
+        <v>123</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F126" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H126" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>138</v>
+        <v>123</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>138</v>
+        <v>5</v>
       </c>
       <c r="E127" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F127" s="6" t="s">
+      <c r="F127" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H127" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>139</v>
+        <v>123</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F128" s="6" t="s">
+      <c r="F128" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H128" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>140</v>
+        <v>123</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F129" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H129" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>141</v>
+        <v>123</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F130" s="6" t="s">
+      <c r="F130" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H130" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>142</v>
+        <v>123</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>142</v>
+        <v>5</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F131" s="6" t="s">
+      <c r="F131" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G131" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H131" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>143</v>
+        <v>123</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>143</v>
+        <v>5</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F132" s="6" t="s">
+      <c r="F132" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G132" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H132" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>144</v>
+        <v>123</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="E133" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F133" s="6" t="s">
+      <c r="F133" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G133" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H133" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>145</v>
+        <v>123</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="F134" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G134" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H134" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>146</v>
+        <v>123</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>146</v>
+        <v>5</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F135" s="6" t="s">
+      <c r="F135" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H135" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>147</v>
+        <v>123</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>147</v>
+        <v>5</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F136" s="6" t="s">
+      <c r="F136" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H136" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H136" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>148</v>
+        <v>123</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="F137" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H137" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>149</v>
+        <v>123</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F138" s="6" t="s">
+      <c r="F138" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G138" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H138" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>150</v>
+        <v>123</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F139" s="6" t="s">
+      <c r="F139" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H139" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>151</v>
+        <v>123</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F140" s="6" t="s">
+      <c r="F140" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H140" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B141" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C141" s="5" t="s">
-        <v>153</v>
+      <c r="C141" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>153</v>
+        <v>5</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F141" s="6" t="s">
+      <c r="F141" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H141" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F142" s="6" t="s">
+      <c r="F142" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H142" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="E143" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F143" s="6" t="s">
+      <c r="F143" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H143" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>156</v>
+        <v>5</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F144" s="6" t="s">
+      <c r="F144" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H144" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>157</v>
+        <v>5</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F145" s="6" t="s">
+      <c r="F145" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H145" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="F146" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H146" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="E147" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F147" s="6" t="s">
+      <c r="F147" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H147" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>160</v>
+        <v>151</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F148" s="6" t="s">
+      <c r="F148" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H148" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>161</v>
+        <v>151</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>161</v>
+        <v>5</v>
       </c>
       <c r="E149" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F149" s="6" t="s">
+      <c r="F149" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H149" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H149" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>162</v>
+        <v>151</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>162</v>
+        <v>5</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F150" s="6" t="s">
+      <c r="F150" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H150" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>163</v>
+        <v>151</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="E151" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F151" s="6" t="s">
+      <c r="F151" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H151" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>164</v>
+        <v>151</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F152" s="6" t="s">
+      <c r="F152" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H152" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>165</v>
+        <v>151</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>165</v>
+        <v>5</v>
       </c>
       <c r="E153" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F153" s="6" t="s">
+      <c r="F153" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H153" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>166</v>
+        <v>151</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>166</v>
+        <v>5</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F154" s="6" t="s">
+      <c r="F154" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H154" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>167</v>
+        <v>151</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>167</v>
+        <v>5</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F155" s="6" t="s">
+      <c r="F155" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H155" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>168</v>
+        <v>151</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>168</v>
+        <v>5</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F156" s="6" t="s">
+      <c r="F156" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H156" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>169</v>
+        <v>151</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>169</v>
+        <v>5</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F157" s="6" t="s">
+      <c r="F157" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H157" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H157" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>170</v>
+        <v>151</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F158" s="6" t="s">
+      <c r="F158" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H158" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H158" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>171</v>
+        <v>151</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>171</v>
+        <v>5</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F159" s="6" t="s">
+      <c r="F159" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H159" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>172</v>
+        <v>151</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>172</v>
+        <v>5</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F160" s="6" t="s">
+      <c r="F160" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H160" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H160" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>173</v>
+        <v>151</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>173</v>
+        <v>5</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F161" s="6" t="s">
+      <c r="F161" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H161" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H161" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>174</v>
+        <v>5</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F162" s="6" t="s">
+      <c r="F162" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H162" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H162" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>175</v>
+        <v>151</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>175</v>
+        <v>5</v>
       </c>
       <c r="E163" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F163" s="6" t="s">
+      <c r="F163" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H163" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H163" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>176</v>
+        <v>151</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>176</v>
+        <v>5</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F164" s="6" t="s">
+      <c r="F164" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H164" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H164" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>177</v>
+        <v>151</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="E165" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F165" s="6" t="s">
+      <c r="F165" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G165" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H165" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H165" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>178</v>
+        <v>151</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>178</v>
+        <v>5</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F166" s="6" t="s">
+      <c r="F166" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H166" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H166" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>179</v>
+        <v>151</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>179</v>
+        <v>5</v>
       </c>
       <c r="E167" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F167" s="6" t="s">
+      <c r="F167" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H167" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H167" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>180</v>
+        <v>151</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F168" s="6" t="s">
+      <c r="F168" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H168" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H168" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>181</v>
+        <v>151</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>180</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>181</v>
+        <v>5</v>
       </c>
       <c r="E169" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F169" s="6" t="s">
+      <c r="F169" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H169" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H169" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>182</v>
+        <v>151</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>181</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F170" s="6" t="s">
+      <c r="F170" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H170" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H170" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>183</v>
+        <v>151</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>182</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>183</v>
+        <v>5</v>
       </c>
       <c r="E171" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F171" s="6" t="s">
+      <c r="F171" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G171" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H171" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H171" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>184</v>
+        <v>151</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>184</v>
+        <v>5</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F172" s="6" t="s">
+      <c r="F172" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H172" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H172" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>185</v>
+        <v>151</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="E173" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F173" s="6" t="s">
+      <c r="F173" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G173" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H173" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H173" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>186</v>
+        <v>151</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>186</v>
+        <v>5</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F174" s="6" t="s">
+      <c r="F174" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G174" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>187</v>
+        <v>151</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>187</v>
+        <v>5</v>
       </c>
       <c r="E175" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F175" s="6" t="s">
+      <c r="F175" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G175" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H175" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H175" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>188</v>
+        <v>151</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>188</v>
+        <v>5</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F176" s="6" t="s">
+      <c r="F176" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G176" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H176" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H176" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>189</v>
+        <v>151</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>189</v>
+        <v>5</v>
       </c>
       <c r="E177" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F177" s="6" t="s">
+      <c r="F177" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G177" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H177" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H177" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>190</v>
+        <v>151</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>190</v>
+        <v>5</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F178" s="6" t="s">
+      <c r="F178" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G178" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H178" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H178" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>191</v>
+        <v>151</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>190</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
       <c r="E179" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F179" s="6" t="s">
+      <c r="F179" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G179" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H179" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>192</v>
+        <v>151</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F180" s="6" t="s">
+      <c r="F180" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H180" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H180" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>193</v>
+        <v>151</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>192</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>193</v>
+        <v>5</v>
       </c>
       <c r="E181" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F181" s="6" t="s">
+      <c r="F181" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H181" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H181" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>194</v>
+        <v>151</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F182" s="6" t="s">
+      <c r="F182" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G182" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H182" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H182" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>195</v>
+        <v>151</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>194</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
       <c r="E183" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F183" s="6" t="s">
+      <c r="F183" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H183" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H183" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>196</v>
+        <v>151</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>196</v>
+        <v>5</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F184" s="6" t="s">
+      <c r="F184" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G184" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H184" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H184" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>197</v>
+        <v>151</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="E185" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F185" s="6" t="s">
+      <c r="F185" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H185" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H185" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>198</v>
+        <v>151</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>198</v>
+        <v>5</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F186" s="6" t="s">
+      <c r="F186" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G186" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H186" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H186" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C187" s="5" t="s">
+      <c r="C187" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E187" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D187" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E187" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F187" s="6" t="s">
-        <v>201</v>
+      <c r="F187" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="G187" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H187" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H187" t="s">
+        <v>391</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" tooltip="Go to MASTER-CS-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483507" xr:uid="{17A5BE65-985E-496A-B2C6-6CADD4EF60BB}"/>
-    <hyperlink ref="C6" r:id="rId2" tooltip="Go to MASTER-CS-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483508" xr:uid="{7BFF93F7-DFE7-4CFB-8A14-8DBD43F7D35D}"/>
-    <hyperlink ref="C7" r:id="rId3" tooltip="Go to MASTER-CS-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483509" xr:uid="{D5BBE40A-F3DE-4009-9711-117296E8C4A4}"/>
-    <hyperlink ref="C8" r:id="rId4" tooltip="Go to MASTER-CS-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483510" xr:uid="{A7B25A8E-79F9-4AF8-8FEE-726E7AE6E48A}"/>
-    <hyperlink ref="C9" r:id="rId5" tooltip="Go to MASTER-CS-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483511" xr:uid="{7285AC82-92FB-4AC3-A422-FD41C95416D4}"/>
-    <hyperlink ref="C10" r:id="rId6" tooltip="Go to MASTER-CS-255-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483512" xr:uid="{9BC94A95-C86D-43DB-BCC5-14C555EA3B29}"/>
-    <hyperlink ref="C11" r:id="rId7" tooltip="Go to MASTER-CS-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483513" xr:uid="{1A57BCC0-F0D5-49DA-B330-D90B28D25D9D}"/>
-    <hyperlink ref="C12" r:id="rId8" tooltip="Go to MASTER-CS-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483514" xr:uid="{48140BD6-9E85-4A87-AF86-D8CE4F9B5E18}"/>
-    <hyperlink ref="C13" r:id="rId9" tooltip="Go to MASTER-CS-305-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483515" xr:uid="{2E2DC389-EF7B-4057-BB91-EA04F52A0C80}"/>
-    <hyperlink ref="C14" r:id="rId10" tooltip="Go to MASTER-CS-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483516" xr:uid="{41751171-8094-45CE-AEDC-E4E8BCF89756}"/>
-    <hyperlink ref="C15" r:id="rId11" tooltip="Go to MASTER-CS-319-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483517" xr:uid="{911AE956-719D-4A87-8AC2-50FBF4D0B443}"/>
-    <hyperlink ref="C16" r:id="rId12" tooltip="Go to MASTER-CS-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483518" xr:uid="{D2E56A80-C40C-4C60-B656-3F20AA0B2278}"/>
-    <hyperlink ref="C17" r:id="rId13" tooltip="Go to MASTER-CS-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483519" xr:uid="{DB3C16CF-85D3-45D8-89D1-E9E0E9DA7298}"/>
-    <hyperlink ref="C18" r:id="rId14" tooltip="Go to MASTER-CS-340-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483520" xr:uid="{3EC155AE-08DD-46D1-B288-82AD54A670D8}"/>
-    <hyperlink ref="C19" r:id="rId15" tooltip="Go to MASTER-CS-350-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483521" xr:uid="{75AECBEE-9DD5-4ED3-BEF6-47A92E45B0CD}"/>
-    <hyperlink ref="C20" r:id="rId16" tooltip="Go to MASTER-CS-360-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483522" xr:uid="{5AC902A0-DF35-431F-B8C2-5D57AA38DDA9}"/>
-    <hyperlink ref="C21" r:id="rId17" tooltip="Go to MASTER-CS-370-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483523" xr:uid="{BA08BDED-F3ED-4B29-A426-531D3C9894EB}"/>
-    <hyperlink ref="C22" r:id="rId18" tooltip="Go to MASTER-CS-405-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483524" xr:uid="{00D6A8EB-98CD-4753-A48C-2EE86005BA9E}"/>
-    <hyperlink ref="C23" r:id="rId19" tooltip="Go to MASTER-CS-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483525" xr:uid="{DFAA7F2C-6D94-42C6-9221-9FB717BC1288}"/>
-    <hyperlink ref="C24" r:id="rId20" tooltip="Go to MASTER-CS-465-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483526" xr:uid="{3F264443-DACF-4419-B65A-FC511BAE0E21}"/>
-    <hyperlink ref="C25" r:id="rId21" tooltip="Go to MASTER-CS-470-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483527" xr:uid="{64E83111-C570-4986-8C60-48E45A1D84E9}"/>
-    <hyperlink ref="C26" r:id="rId22" tooltip="Go to MASTER-CS-499-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483528" xr:uid="{B722E6B6-5E14-4A1D-9D5F-3B7CE6C969AE}"/>
-    <hyperlink ref="C71" r:id="rId23" tooltip="Go to MASTER-IT-100-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483815" xr:uid="{11DFDDAF-5834-4BE3-957E-43666F824E38}"/>
-    <hyperlink ref="C2" r:id="rId24" tooltip="Go to MASTER-IT-140-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483816" xr:uid="{A854194D-A016-4B8E-9CD4-0199E9D058B1}"/>
-    <hyperlink ref="C3" r:id="rId25" tooltip="Go to MASTER-IT-145-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483817" xr:uid="{2F48F9C2-CF0F-45D1-BEAD-082AA769B618}"/>
-    <hyperlink ref="C72" r:id="rId26" tooltip="Go to MASTER-IT-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483818" xr:uid="{2641FC39-82B9-4EAD-925A-E7438719ACB9}"/>
-    <hyperlink ref="C73" r:id="rId27" tooltip="Go to MASTER-IT-202-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483819" xr:uid="{5196EE07-E0C3-4ECB-84BA-FB502943EB38}"/>
-    <hyperlink ref="C74" r:id="rId28" tooltip="Go to MASTER-IT-204-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483820" xr:uid="{B6D557EC-2AAB-48EF-AF12-71E5AC839A28}"/>
-    <hyperlink ref="C75" r:id="rId29" tooltip="Go to MASTER-IT-209-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483821" xr:uid="{B38B6B28-67D2-4AFD-9BD0-BA0AAB37775E}"/>
-    <hyperlink ref="C76" r:id="rId30" tooltip="Go to MASTER-IT-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483822" xr:uid="{9825AC83-B6B4-45CE-AADA-C61DFD06876A}"/>
-    <hyperlink ref="C77" r:id="rId31" tooltip="Go to MASTER-IT-212-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483823" xr:uid="{83F2D244-802A-4326-96EC-CC3FCA011959}"/>
-    <hyperlink ref="C78" r:id="rId32" tooltip="Go to MASTER-IT-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483824" xr:uid="{CF08E656-26BD-4FF2-A4D0-CAACB2FBC542}"/>
-    <hyperlink ref="C79" r:id="rId33" tooltip="Go to MASTER-IT-216-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483825" xr:uid="{22A443A1-9B83-479B-A3A7-2BFAC0838BC8}"/>
-    <hyperlink ref="C80" r:id="rId34" tooltip="Go to MASTER-IT-217-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483826" xr:uid="{34940FB5-197C-41D4-862F-778E2E798F4B}"/>
-    <hyperlink ref="C81" r:id="rId35" tooltip="Go to MASTER-IT-226-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483827" xr:uid="{662D5C9F-A362-4F3F-AEC4-BB2741B417C8}"/>
-    <hyperlink ref="C82" r:id="rId36" tooltip="Go to MASTER-IT-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483828" xr:uid="{1EAB80D6-2C15-4B6C-9BB7-D45BA010C0EA}"/>
-    <hyperlink ref="C83" r:id="rId37" tooltip="Go to MASTER-IT-235-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483829" xr:uid="{EB22C54A-4DB0-4B86-918F-AE5A651DE12A}"/>
-    <hyperlink ref="C84" r:id="rId38" tooltip="Go to MASTER-IT-241-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483830" xr:uid="{24F6C96F-BC9A-4427-8EB5-0A18F81286B5}"/>
-    <hyperlink ref="C85" r:id="rId39" tooltip="Go to MASTER-IT-242-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483831" xr:uid="{F07E212A-742B-45DE-ABA4-A011D8A39A9D}"/>
-    <hyperlink ref="C86" r:id="rId40" tooltip="Go to MASTER-IT-252-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483832" xr:uid="{EC042BA1-1607-4683-BDD3-23DB9EC7A0D0}"/>
-    <hyperlink ref="C87" r:id="rId41" tooltip="Go to MASTER-IT-253-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483833" xr:uid="{DA17C027-B502-49F7-A0AD-0F2F0B6C3B30}"/>
-    <hyperlink ref="C88" r:id="rId42" tooltip="Go to MASTER-IT-255-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483834" xr:uid="{977D9AD0-6044-4DF6-9016-BB6D89825017}"/>
-    <hyperlink ref="C89" r:id="rId43" tooltip="Go to MASTER-IT-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483835" xr:uid="{E4C1F23C-46B4-49F0-A494-53D7CA03C9B5}"/>
-    <hyperlink ref="C90" r:id="rId44" tooltip="Go to MASTER-IT-261-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483836" xr:uid="{D3C891B0-454D-4D17-B10E-F4DFB75E6132}"/>
-    <hyperlink ref="C91" r:id="rId45" tooltip="Go to MASTER-IT-270-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483837" xr:uid="{5B9DF672-DED3-401C-80B0-93D6A4480F37}"/>
-    <hyperlink ref="C92" r:id="rId46" tooltip="Go to MASTER-IT-272-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483838" xr:uid="{1059878A-F977-4DCB-8E3F-FE693A38811B}"/>
-    <hyperlink ref="C93" r:id="rId47" tooltip="Go to MASTER-IT-304-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483839" xr:uid="{DCE403E5-7D31-4960-8B9C-9AF327A362E0}"/>
-    <hyperlink ref="C94" r:id="rId48" tooltip="Go to MASTER-IT-312-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483840" xr:uid="{B6A81AAC-22D4-4C99-9B81-6A752FCCF21B}"/>
-    <hyperlink ref="C95" r:id="rId49" tooltip="Go to MASTER-IT-313-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483841" xr:uid="{68310F40-F60E-4098-9633-5346BC4AE60A}"/>
-    <hyperlink ref="C96" r:id="rId50" tooltip="Go to MASTER-IT-315-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483842" xr:uid="{C0E5EFAA-9AA9-4EC3-ADCE-DC53028E8B53}"/>
-    <hyperlink ref="C97" r:id="rId51" tooltip="Go to MASTER-IT-328-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483843" xr:uid="{8FAE7361-7E01-4E4E-A09F-10B386112A36}"/>
-    <hyperlink ref="C98" r:id="rId52" tooltip="Go to MASTER-IT-331-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483844" xr:uid="{5050112C-8451-4B9C-9999-6924255653A9}"/>
-    <hyperlink ref="C99" r:id="rId53" tooltip="Go to MASTER-IT-332-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483845" xr:uid="{DA86CE2B-A5DA-4671-884C-BFE0B6E153F5}"/>
-    <hyperlink ref="C100" r:id="rId54" tooltip="Go to MASTER-IT-337-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483846" xr:uid="{8653F8A8-5176-48C3-AF72-E9E303EDD79B}"/>
-    <hyperlink ref="C101" r:id="rId55" tooltip="Go to MASTER-IT-338-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483847" xr:uid="{C227140B-0AE4-4F36-B1F0-E396DCB8EE3A}"/>
-    <hyperlink ref="C102" r:id="rId56" tooltip="Go to MASTER-IT-345-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483848" xr:uid="{EFB3AD74-D60F-4BC2-A2AF-790DD022F3E4}"/>
-    <hyperlink ref="C103" r:id="rId57" tooltip="Go to MASTER-IT-355-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483849" xr:uid="{E9A0F36C-068C-4862-BEED-2B5EFB311923}"/>
-    <hyperlink ref="C104" r:id="rId58" tooltip="Go to MASTER-IT-365-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483850" xr:uid="{E0474831-7B8B-4015-B6BC-EA48A5B34269}"/>
-    <hyperlink ref="C105" r:id="rId59" tooltip="Go to MASTER-IT-390-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483851" xr:uid="{829D471E-7E49-41B7-87CA-C568DC7404A4}"/>
-    <hyperlink ref="C106" r:id="rId60" tooltip="Go to MASTER-IT-409-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483852" xr:uid="{6637F63D-A68E-4FA9-92A8-2738C4D41F3E}"/>
-    <hyperlink ref="C107" r:id="rId61" tooltip="Go to MASTER-IT-415-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483853" xr:uid="{19EEA6D4-3477-4AB0-8D6C-3708718630B9}"/>
-    <hyperlink ref="C108" r:id="rId62" tooltip="Go to MASTER-IT-420-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483854" xr:uid="{813128B3-4162-401A-89F5-EC0920E96E3F}"/>
-    <hyperlink ref="C109" r:id="rId63" tooltip="Go to MASTER-IT-423-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483855" xr:uid="{79AEDCBF-18F2-4167-B7A8-F19E11047037}"/>
-    <hyperlink ref="C110" r:id="rId64" tooltip="Go to MASTER-IT-450-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483856" xr:uid="{CCF9D67E-A8C9-4198-92EE-DDE892BF9270}"/>
-    <hyperlink ref="C111" r:id="rId65" tooltip="Go to MASTER-IT-460-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483857" xr:uid="{71506836-233F-4B1E-AC6A-D3D4CC6AEDDE}"/>
-    <hyperlink ref="C112" r:id="rId66" tooltip="Go to MASTER-IT-482-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483858" xr:uid="{8AAD6312-FFC1-4331-9CF6-FAD0E6C8468D}"/>
-    <hyperlink ref="C113" r:id="rId67" tooltip="Go to MASTER-IT-489-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483859" xr:uid="{AAA9D89A-5308-4284-BE5E-2B94302AA74B}"/>
-    <hyperlink ref="C187" r:id="rId68" tooltip="Go to MASTER-DAD-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483542" xr:uid="{B62ADAC3-689A-4F6C-BACF-DB2366E2FF6A}"/>
-    <hyperlink ref="C4" r:id="rId69" tooltip="Go to MASTER-DAD-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483543" xr:uid="{49033D59-3581-49FD-95DC-C9F09EEEE54E}"/>
-    <hyperlink ref="C55" r:id="rId70" tooltip="Go to MASTER-GAM-120-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483641" xr:uid="{0C41175B-9D42-4E45-837F-EE6B236F6EB5}"/>
-    <hyperlink ref="C56" r:id="rId71" tooltip="Go to MASTER-GAM-207-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483642" xr:uid="{91422D81-07D6-4BF5-BA43-A3F9024C4318}"/>
-    <hyperlink ref="C57" r:id="rId72" tooltip="Go to MASTER-GAM-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483643" xr:uid="{466AC651-F779-464E-9D04-5AEC01D5550F}"/>
-    <hyperlink ref="C58" r:id="rId73" tooltip="Go to MASTER-GAM-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483644" xr:uid="{6DAE3D1E-B2F1-4CA1-AF10-EE8C0D7D87E7}"/>
-    <hyperlink ref="C59" r:id="rId74" tooltip="Go to MASTER-GAM-303-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483645" xr:uid="{2E571C33-79FD-46DF-AF7C-4C039C54D697}"/>
-    <hyperlink ref="C60" r:id="rId75" tooltip="Go to MASTER-GAM-305-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483646" xr:uid="{0874430D-0CD1-4D89-9B55-BCDE4FDA02FE}"/>
-    <hyperlink ref="C61" r:id="rId76" tooltip="Go to MASTER-GAM-312-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483647" xr:uid="{C5FEE379-8AF3-4417-ADE4-57044961E383}"/>
-    <hyperlink ref="C62" r:id="rId77" tooltip="Go to MASTER-GAM-315-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2441925" xr:uid="{1A3E48FF-E145-4FDA-8922-65D7EFFD35C7}"/>
-    <hyperlink ref="C63" r:id="rId78" tooltip="Go to MASTER-GAM-325-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483648" xr:uid="{6E693B01-D331-4A28-9566-C0788E5EE1B8}"/>
-    <hyperlink ref="C64" r:id="rId79" tooltip="Go to MASTER-GAM-335-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2374297" xr:uid="{6C210166-B628-4A1E-968F-B623B7519EBB}"/>
-    <hyperlink ref="C65" r:id="rId80" tooltip="Go to MASTER-GAM-355-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2441926" xr:uid="{DC299028-DB20-497B-8D28-42C868EF139D}"/>
-    <hyperlink ref="C66" r:id="rId81" tooltip="Go to MASTER-GAM-360-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2374299" xr:uid="{376B7A00-734D-490D-B5A9-E1CC510C4514}"/>
-    <hyperlink ref="C67" r:id="rId82" tooltip="Go to MASTER-GAM-380-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483649" xr:uid="{6E9602FB-5D6F-4CF7-97C0-F0B96FFDDB21}"/>
-    <hyperlink ref="C68" r:id="rId83" tooltip="Go to MASTER-GAM-415-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483650" xr:uid="{3C4B77C6-0D84-4C23-B89E-EC49EB9B882E}"/>
-    <hyperlink ref="C69" r:id="rId84" tooltip="Go to MASTER-GAM-465-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483651" xr:uid="{FDBFACD5-4B44-43B5-AE83-34C5A73B3FA3}"/>
-    <hyperlink ref="C70" r:id="rId85" tooltip="Go to MASTER-GAM-495-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483652" xr:uid="{27A26686-8002-45A2-B8F9-437A308885CD}"/>
-    <hyperlink ref="C27" r:id="rId86" tooltip="Go to MASTER-CYB-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483529" xr:uid="{7432F9C9-3EF3-4ECB-8BB4-78C280EA7AED}"/>
-    <hyperlink ref="C28" r:id="rId87" tooltip="Go to MASTER-CYB-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483530" xr:uid="{4E09C76E-8783-44BF-AB2B-69013B0A5720}"/>
-    <hyperlink ref="C29" r:id="rId88" tooltip="Go to MASTER-CYB-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483531" xr:uid="{A5FE08F6-00C8-4BF1-9DA8-3E2A9764420F}"/>
-    <hyperlink ref="C30" r:id="rId89" tooltip="Go to MASTER-CYB-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483532" xr:uid="{5DA48EB2-CFE3-435B-BBE8-F7C4E5F206BC}"/>
-    <hyperlink ref="C31" r:id="rId90" tooltip="Go to MASTER-CYB-240-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483533" xr:uid="{1CA83868-56FA-4CC8-8832-6B6C78545ACF}"/>
-    <hyperlink ref="C32" r:id="rId91" tooltip="Go to MASTER-CYB-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483534" xr:uid="{4B485320-3C65-4E1B-AF2F-41E8E561DFF9}"/>
-    <hyperlink ref="C33" r:id="rId92" tooltip="Go to MASTER-CYB-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483535" xr:uid="{ED07A184-97BF-40EB-98CB-B39F0D4212F8}"/>
-    <hyperlink ref="C34" r:id="rId93" tooltip="Go to MASTER-CYB-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483536" xr:uid="{CC9AA3DB-1A7D-495E-B1CF-FF5D46B15720}"/>
-    <hyperlink ref="C35" r:id="rId94" tooltip="Go to MASTER-CYB-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483537" xr:uid="{1871879D-378F-4D51-936E-7FAA86BE02E1}"/>
-    <hyperlink ref="C36" r:id="rId95" tooltip="Go to MASTER-CYB-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483538" xr:uid="{16515BEA-AC8D-4D42-8D45-E2DE90BD1C55}"/>
-    <hyperlink ref="C37" r:id="rId96" tooltip="Go to MASTER-CYB-400-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483539" xr:uid="{D0CE0155-EAC7-459B-AE75-CD9B89AECA2C}"/>
-    <hyperlink ref="C38" r:id="rId97" tooltip="Go to MASTER-CYB-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483540" xr:uid="{41D2B323-290C-4373-8590-19A39A945914}"/>
-    <hyperlink ref="C39" r:id="rId98" tooltip="Go to MASTER-CYB-420-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483541" xr:uid="{64AD183A-951E-4F8B-9789-970EB8D4C72A}"/>
-    <hyperlink ref="C114" r:id="rId99" tooltip="Go to MASTER-MAT-125-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483888" xr:uid="{8CDCBF5F-0215-4432-9860-270AE868D281}"/>
-    <hyperlink ref="C115" r:id="rId100" tooltip="Go to MASTER-MAT-126-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483889" xr:uid="{FF00D006-1156-4264-9FB9-5C552B3D8AC4}"/>
-    <hyperlink ref="C116" r:id="rId101" tooltip="Go to MASTER-MAT-130-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483890" xr:uid="{70134E33-C160-4475-8707-B6552105A776}"/>
-    <hyperlink ref="C117" r:id="rId102" tooltip="Go to MASTER-MAT-133-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483891" xr:uid="{680D9F30-6AE7-4E64-9E5E-46A5F014F021}"/>
-    <hyperlink ref="C118" r:id="rId103" tooltip="Go to MASTER-MAT-135-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483892" xr:uid="{1861FE2E-5399-46EA-B6E8-67B0C3638E3F}"/>
-    <hyperlink ref="C119" r:id="rId104" tooltip="Go to MASTER-MAT-136-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483893" xr:uid="{09677CC7-A202-4DDF-8C82-8EB98D2ED8F9}"/>
-    <hyperlink ref="C120" r:id="rId105" tooltip="Go to MASTER-MAT-140-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483894" xr:uid="{EABF214B-F932-4EAB-B632-3EE7B05C4AB8}"/>
-    <hyperlink ref="C121" r:id="rId106" tooltip="Go to MASTER-MAT-142-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483895" xr:uid="{4D62A1D2-D965-4451-80EB-8CA4AE8C1CE4}"/>
-    <hyperlink ref="C122" r:id="rId107" tooltip="Go to MASTER-MAT-225-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483896" xr:uid="{1425ABA6-C70B-4549-A0F1-377A6D3DB938}"/>
-    <hyperlink ref="C123" r:id="rId108" tooltip="Go to MASTER-MAT-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483897" xr:uid="{BACA5C0E-A64E-4145-84C4-39145908B411}"/>
-    <hyperlink ref="C124" r:id="rId109" tooltip="Go to MASTER-MAT-240-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483898" xr:uid="{2D971353-6D36-413F-95AA-68EA08FEA80F}"/>
-    <hyperlink ref="C125" r:id="rId110" tooltip="Go to MASTER-MAT-243-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483899" xr:uid="{CD299913-81B8-4841-A16B-27D8E4405B87}"/>
-    <hyperlink ref="C126" r:id="rId111" tooltip="Go to MASTER-MAT-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483900" xr:uid="{E1954F85-F13C-42C0-9AC2-FF99791962D8}"/>
-    <hyperlink ref="C127" r:id="rId112" tooltip="Go to MASTER-MAT-275-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483901" xr:uid="{813D7C5E-B930-4589-A85B-4F65A3A63195}"/>
-    <hyperlink ref="C128" r:id="rId113" tooltip="Go to MASTER-MAT-299-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483902" xr:uid="{E5835416-A7B8-483E-BA3B-593920C5332D}"/>
-    <hyperlink ref="C129" r:id="rId114" tooltip="Go to MASTER-MAT-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483903" xr:uid="{799AFF61-62E1-40C6-878D-478876A9B3ED}"/>
-    <hyperlink ref="C130" r:id="rId115" tooltip="Go to MASTER-MAT-303-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483904" xr:uid="{456545BE-2F5A-4F7E-B309-EFC999CA35CE}"/>
-    <hyperlink ref="C131" r:id="rId116" tooltip="Go to MASTER-MAT-325-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483905" xr:uid="{BDCF02A3-467A-490C-909B-80CA5ACB89D5}"/>
-    <hyperlink ref="C132" r:id="rId117" tooltip="Go to MASTER-MAT-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483906" xr:uid="{27ECB989-62C2-4DB8-915E-0AD137B7C000}"/>
-    <hyperlink ref="C133" r:id="rId118" tooltip="Go to MASTER-MAT-350-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483907" xr:uid="{E483ABFC-2AC5-426F-B894-0AADF110AE6E}"/>
-    <hyperlink ref="C134" r:id="rId119" tooltip="Go to MASTER-MAT-375-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483908" xr:uid="{7A9E3618-A4E9-4C96-A90F-246205CE2F0E}"/>
-    <hyperlink ref="C135" r:id="rId120" tooltip="Go to MASTER-MAT-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483909" xr:uid="{BF2F601A-4761-45FF-8F81-83415FAE76B4}"/>
-    <hyperlink ref="C136" r:id="rId121" tooltip="Go to MASTER-MAT-415-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483910" xr:uid="{7166DFE2-9BB7-4931-8434-D4F679D38CDC}"/>
-    <hyperlink ref="C137" r:id="rId122" tooltip="Go to MASTER-MAT-420-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483911" xr:uid="{2DA42189-C18C-4DA6-B5B5-1D3C5AD20682}"/>
-    <hyperlink ref="C138" r:id="rId123" tooltip="Go to MASTER-MAT-430-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483912" xr:uid="{CB3152D7-6876-4CBA-B821-AE7E47AA3F24}"/>
-    <hyperlink ref="C139" r:id="rId124" tooltip="Go to MASTER-MAT-450-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483913" xr:uid="{673E9DD6-FA7C-40C8-BC67-7CA48B278F26}"/>
-    <hyperlink ref="C140" r:id="rId125" tooltip="Go to MASTER-MAT-470-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483914" xr:uid="{2BD55DEF-ACAD-4DE8-97E8-22C687F97858}"/>
-    <hyperlink ref="C163" r:id="rId126" tooltip="Go to MASTER-PHY-101-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484016" xr:uid="{8D6D42AE-CD16-428F-A13B-CF6938CEB691}"/>
-    <hyperlink ref="C164" r:id="rId127" tooltip="Go to MASTER-PHY-101L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484017" xr:uid="{9D86C117-C887-4FC8-9788-2874B7CEFC04}"/>
-    <hyperlink ref="C165" r:id="rId128" tooltip="Go to MASTER-PHY-103-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484018" xr:uid="{B3E66FA6-F823-4012-AC26-A789D411B912}"/>
-    <hyperlink ref="C166" r:id="rId129" tooltip="Go to MASTER-PHY-105-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484019" xr:uid="{2E0560AB-641E-4525-B345-A63319ED0029}"/>
-    <hyperlink ref="C167" r:id="rId130" tooltip="Go to MASTER-PHY-150-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484020" xr:uid="{9B232A33-F008-4005-9439-7575D16EB3D2}"/>
-    <hyperlink ref="C168" r:id="rId131" tooltip="Go to MASTER-PHY-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484021" xr:uid="{4B791B6D-AA47-4327-9C7D-03E08A104555}"/>
-    <hyperlink ref="C169" r:id="rId132" tooltip="Go to MASTER-PHY-205L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484022" xr:uid="{B3CB2E30-E2BC-4453-9A88-B8EBC39F040C}"/>
-    <hyperlink ref="C40" r:id="rId133" tooltip="Go to MASTER-DAT-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483544" xr:uid="{F809EB20-E9BC-49B8-B68A-BC917B695673}"/>
-    <hyperlink ref="C41" r:id="rId134" tooltip="Go to MASTER-DAT-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483545" xr:uid="{D80A8745-285B-41E3-AB02-7AB5438051A2}"/>
-    <hyperlink ref="C42" r:id="rId135" tooltip="Go to MASTER-DAT-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483546" xr:uid="{D7977F02-8867-4E9A-9A2A-7F63D958FB35}"/>
-    <hyperlink ref="C43" r:id="rId136" tooltip="Go to MASTER-DAT-223-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483547" xr:uid="{643B0DC2-BE46-452B-8E57-BEF1EDF2AD64}"/>
-    <hyperlink ref="C44" r:id="rId137" tooltip="Go to MASTER-DAT-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483548" xr:uid="{26B3BE76-983D-4383-AD0C-D6AF38484C6C}"/>
-    <hyperlink ref="C45" r:id="rId138" tooltip="Go to MASTER-DAT-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483549" xr:uid="{CE1A388F-8F09-483C-A2E2-819ADED15167}"/>
-    <hyperlink ref="C46" r:id="rId139" tooltip="Go to MASTER-DAT-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483550" xr:uid="{4377332A-B6CA-43A9-B420-7452BC46D0AB}"/>
-    <hyperlink ref="C47" r:id="rId140" tooltip="Go to MASTER-DAT-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483551" xr:uid="{D58509E3-4B98-4B9B-AFC3-44FA29F7FF69}"/>
-    <hyperlink ref="C48" r:id="rId141" tooltip="Go to MASTER-DAT-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483552" xr:uid="{ED590D1A-4987-4CD9-9F25-B613321B7A3A}"/>
-    <hyperlink ref="C49" r:id="rId142" tooltip="Go to MASTER-DAT-325-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483553" xr:uid="{4617C594-BA42-41EE-A398-C79EA590E630}"/>
-    <hyperlink ref="C50" r:id="rId143" tooltip="Go to MASTER-DAT-375-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483554" xr:uid="{4F94CAA0-F5FC-4FCF-B12F-C306B09C421C}"/>
-    <hyperlink ref="C51" r:id="rId144" tooltip="Go to MASTER-DAT-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483555" xr:uid="{946543D5-E01C-4895-AC6B-517ED1EC7BC7}"/>
-    <hyperlink ref="C52" r:id="rId145" tooltip="Go to MASTER-DAT-430-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483556" xr:uid="{5A4CC67F-A231-4681-A052-0B00ABC13BF2}"/>
-    <hyperlink ref="C53" r:id="rId146" tooltip="Go to MASTER-DAT-475-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483557" xr:uid="{B43A6170-90F4-4A6E-A3DB-85565598BF56}"/>
-    <hyperlink ref="C54" r:id="rId147" tooltip="Go to MASTER-DAT-490-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483558" xr:uid="{06A36F06-3021-40AF-94F4-24828F193F54}"/>
-    <hyperlink ref="C141" r:id="rId148" tooltip="Go to MASTER-BIO-120-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483406" xr:uid="{1A85F4C2-734F-40BD-8749-1632EC503F1B}"/>
-    <hyperlink ref="C142" r:id="rId149" tooltip="Go to MASTER-BIO-120L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483407" xr:uid="{2386945F-CE29-4F8A-A81D-DCD0AE2C1C78}"/>
-    <hyperlink ref="C143" r:id="rId150" tooltip="Go to MASTER-BIO-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483408" xr:uid="{2B6C8B1F-0269-45D5-A056-3FD89617E470}"/>
-    <hyperlink ref="C144" r:id="rId151" tooltip="Go to MASTER-BIO-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483409" xr:uid="{31CE2608-9B97-4569-BA9B-3C1787FE6309}"/>
-    <hyperlink ref="C145" r:id="rId152" tooltip="Go to MASTER-BIO-211-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483410" xr:uid="{08367A92-A988-4A9C-B4F6-B2E091A36042}"/>
-    <hyperlink ref="C146" r:id="rId153" tooltip="Go to MASTER-BIO-212-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483411" xr:uid="{04779CE1-3EBD-494D-98D4-FF56FEF17C0D}"/>
-    <hyperlink ref="C147" r:id="rId154" tooltip="Go to MASTER-BIO-315-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483412" xr:uid="{38765AC3-2133-4568-B032-1D4418C3A5BA}"/>
-    <hyperlink ref="C148" r:id="rId155" tooltip="Go to MASTER-BIO-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483413" xr:uid="{259A90C3-DF76-422A-9F70-06B9FA8E7377}"/>
-    <hyperlink ref="C149" r:id="rId156" tooltip="Go to MASTER-CHM-101-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483434" xr:uid="{1C7B820A-6F8C-49E9-8A91-B4DDBF14F236}"/>
-    <hyperlink ref="C150" r:id="rId157" tooltip="Go to MASTER-CHM-101L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483435" xr:uid="{17B1EA1E-382A-4E89-94CC-E3E284BA5CF1}"/>
-    <hyperlink ref="C151" r:id="rId158" tooltip="Go to MASTER-ENV-101-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483589" xr:uid="{A447EB88-5A10-4AEA-B0AE-35DA169109A2}"/>
-    <hyperlink ref="C152" r:id="rId159" tooltip="Go to MASTER-ENV-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483590" xr:uid="{52CFF6AD-B69E-42A5-B758-3D35DDD50312}"/>
-    <hyperlink ref="C153" r:id="rId160" tooltip="Go to MASTER-ENV-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483591" xr:uid="{94A869A4-9F0C-435E-B634-4020B170B58C}"/>
-    <hyperlink ref="C154" r:id="rId161" tooltip="Go to MASTER-ENV-280-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483592" xr:uid="{BDE77CEE-8A2F-4F48-B21B-21A72C9C6144}"/>
-    <hyperlink ref="C155" r:id="rId162" tooltip="Go to MASTER-ENV-305-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483593" xr:uid="{5166CC6E-A4BA-46B9-9CF9-DBA325A5F73E}"/>
-    <hyperlink ref="C156" r:id="rId163" tooltip="Go to MASTER-ENV-319-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483594" xr:uid="{53FF6D9B-EEA2-4D30-BA16-5D120D1F2568}"/>
-    <hyperlink ref="C157" r:id="rId164" tooltip="Go to MASTER-ENV-361-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483595" xr:uid="{870C2430-8AD6-4AB5-9B28-8A405A3A7B79}"/>
-    <hyperlink ref="C158" r:id="rId165" tooltip="Go to MASTER-ENV-440-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483596" xr:uid="{BF1A9F12-D39B-4180-A75E-F8D57C4F521C}"/>
-    <hyperlink ref="C159" r:id="rId166" tooltip="Go to MASTER-GEO-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483655" xr:uid="{A0057BD4-9F6B-4790-AA97-1FA0037C8214}"/>
-    <hyperlink ref="C160" r:id="rId167" tooltip="Go to MASTER-GEO-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483656" xr:uid="{87BA3298-695F-4BD5-ADF4-CDDA984AB001}"/>
-    <hyperlink ref="C161" r:id="rId168" tooltip="Go to MASTER-GEO-345-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483657" xr:uid="{68AC775B-1874-4D4F-8E25-1BF024AD96CA}"/>
-    <hyperlink ref="C162" r:id="rId169" tooltip="Go to MASTER-GEO-450-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483658" xr:uid="{299D78A2-B69B-4557-92DC-F00727430D69}"/>
-    <hyperlink ref="C170" r:id="rId170" tooltip="Go to MASTER-SCI-100-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484113" xr:uid="{095BE097-D2D1-4D58-986D-072F6A917F39}"/>
-    <hyperlink ref="C171" r:id="rId171" tooltip="Go to MASTER-SCI-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484114" xr:uid="{D91E72CC-7791-48AB-BC1B-6E1B17E38590}"/>
-    <hyperlink ref="C172" r:id="rId172" tooltip="Go to MASTER-SCI-207-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484115" xr:uid="{A0D561D9-184E-473F-924C-8715E771D765}"/>
-    <hyperlink ref="C173" r:id="rId173" tooltip="Go to MASTER-SCI-212-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484116" xr:uid="{2106654A-1851-4F0C-8CD4-83EFD298C15B}"/>
-    <hyperlink ref="C174" r:id="rId174" tooltip="Go to MASTER-SCI-214-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484117" xr:uid="{D140712F-6DBD-49AE-A499-2697137DAF06}"/>
-    <hyperlink ref="C175" r:id="rId175" tooltip="Go to MASTER-SCI-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484118" xr:uid="{B801697F-80C5-470B-9079-DFD752B4FA7C}"/>
-    <hyperlink ref="C176" r:id="rId176" tooltip="Go to MASTER-SCI-218-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484119" xr:uid="{5A00CB28-95CB-442E-8390-876BFD1F764F}"/>
-    <hyperlink ref="C177" r:id="rId177" tooltip="Go to MASTER-SCI-219-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484120" xr:uid="{48A979D8-2B84-4B85-BEA9-0A1313988436}"/>
-    <hyperlink ref="C178" r:id="rId178" tooltip="Go to MASTER-SCI-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484121" xr:uid="{F60AB33D-13FC-4B55-94A3-D384DCAD4045}"/>
-    <hyperlink ref="C179" r:id="rId179" tooltip="Go to MASTER-SCI-225-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484122" xr:uid="{141D2663-BEFA-47FA-837F-E0978D57B5E1}"/>
-    <hyperlink ref="C180" r:id="rId180" tooltip="Go to MASTER-SCI-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484123" xr:uid="{11456F76-E0BF-4B36-AC20-383D377CDD7E}"/>
-    <hyperlink ref="C181" r:id="rId181" tooltip="Go to MASTER-SCI-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484124" xr:uid="{4A1EC514-B6D6-492C-9BCB-2F7B2DF78843}"/>
-    <hyperlink ref="C182" r:id="rId182" tooltip="Go to MASTER-SCI-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484125" xr:uid="{B09612BC-C632-42C8-A891-B7F58AC7CF61}"/>
-    <hyperlink ref="C183" r:id="rId183" tooltip="Go to MASTER-SCI-333-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484126" xr:uid="{88ADFB7C-030D-46B2-9F8D-5DCC37958617}"/>
-    <hyperlink ref="C184" r:id="rId184" tooltip="Go to MASTER-SCI-350-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484127" xr:uid="{B2C2AA2C-291F-4D46-80B3-17C2A3569312}"/>
-    <hyperlink ref="C185" r:id="rId185" tooltip="Go to MASTER-SCI-425-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484128" xr:uid="{9710237F-394A-41B7-B1A5-A610CC5CBAAE}"/>
-    <hyperlink ref="C186" r:id="rId186" tooltip="Go to MASTER-SCI-489-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484129" xr:uid="{BFB4BE87-8336-4648-96AA-AF57E37E1D66}"/>
+    <hyperlink ref="B5" r:id="rId1" tooltip="Go to MASTER-CS-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483507" xr:uid="{17A5BE65-985E-496A-B2C6-6CADD4EF60BB}"/>
+    <hyperlink ref="B6" r:id="rId2" tooltip="Go to MASTER-CS-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483508" xr:uid="{7BFF93F7-DFE7-4CFB-8A14-8DBD43F7D35D}"/>
+    <hyperlink ref="B7" r:id="rId3" tooltip="Go to MASTER-CS-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483509" xr:uid="{D5BBE40A-F3DE-4009-9711-117296E8C4A4}"/>
+    <hyperlink ref="B8" r:id="rId4" tooltip="Go to MASTER-CS-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483510" xr:uid="{A7B25A8E-79F9-4AF8-8FEE-726E7AE6E48A}"/>
+    <hyperlink ref="B9" r:id="rId5" tooltip="Go to MASTER-CS-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483511" xr:uid="{7285AC82-92FB-4AC3-A422-FD41C95416D4}"/>
+    <hyperlink ref="B10" r:id="rId6" tooltip="Go to MASTER-CS-255-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483512" xr:uid="{9BC94A95-C86D-43DB-BCC5-14C555EA3B29}"/>
+    <hyperlink ref="B11" r:id="rId7" tooltip="Go to MASTER-CS-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483513" xr:uid="{1A57BCC0-F0D5-49DA-B330-D90B28D25D9D}"/>
+    <hyperlink ref="B12" r:id="rId8" tooltip="Go to MASTER-CS-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483514" xr:uid="{48140BD6-9E85-4A87-AF86-D8CE4F9B5E18}"/>
+    <hyperlink ref="B13" r:id="rId9" tooltip="Go to MASTER-CS-305-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483515" xr:uid="{2E2DC389-EF7B-4057-BB91-EA04F52A0C80}"/>
+    <hyperlink ref="B14" r:id="rId10" tooltip="Go to MASTER-CS-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483516" xr:uid="{41751171-8094-45CE-AEDC-E4E8BCF89756}"/>
+    <hyperlink ref="B15" r:id="rId11" tooltip="Go to MASTER-CS-319-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483517" xr:uid="{911AE956-719D-4A87-8AC2-50FBF4D0B443}"/>
+    <hyperlink ref="B16" r:id="rId12" tooltip="Go to MASTER-CS-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483518" xr:uid="{D2E56A80-C40C-4C60-B656-3F20AA0B2278}"/>
+    <hyperlink ref="B17" r:id="rId13" tooltip="Go to MASTER-CS-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483519" xr:uid="{DB3C16CF-85D3-45D8-89D1-E9E0E9DA7298}"/>
+    <hyperlink ref="B18" r:id="rId14" tooltip="Go to MASTER-CS-340-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483520" xr:uid="{3EC155AE-08DD-46D1-B288-82AD54A670D8}"/>
+    <hyperlink ref="B19" r:id="rId15" tooltip="Go to MASTER-CS-350-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483521" xr:uid="{75AECBEE-9DD5-4ED3-BEF6-47A92E45B0CD}"/>
+    <hyperlink ref="B20" r:id="rId16" tooltip="Go to MASTER-CS-360-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483522" xr:uid="{5AC902A0-DF35-431F-B8C2-5D57AA38DDA9}"/>
+    <hyperlink ref="B21" r:id="rId17" tooltip="Go to MASTER-CS-370-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483523" xr:uid="{BA08BDED-F3ED-4B29-A426-531D3C9894EB}"/>
+    <hyperlink ref="B22" r:id="rId18" tooltip="Go to MASTER-CS-405-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483524" xr:uid="{00D6A8EB-98CD-4753-A48C-2EE86005BA9E}"/>
+    <hyperlink ref="B23" r:id="rId19" tooltip="Go to MASTER-CS-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483525" xr:uid="{DFAA7F2C-6D94-42C6-9221-9FB717BC1288}"/>
+    <hyperlink ref="B24" r:id="rId20" tooltip="Go to MASTER-CS-465-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483526" xr:uid="{3F264443-DACF-4419-B65A-FC511BAE0E21}"/>
+    <hyperlink ref="B25" r:id="rId21" tooltip="Go to MASTER-CS-470-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483527" xr:uid="{64E83111-C570-4986-8C60-48E45A1D84E9}"/>
+    <hyperlink ref="B26" r:id="rId22" tooltip="Go to MASTER-CS-499-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483528" xr:uid="{B722E6B6-5E14-4A1D-9D5F-3B7CE6C969AE}"/>
+    <hyperlink ref="B71" r:id="rId23" tooltip="Go to MASTER-IT-100-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483815" xr:uid="{11DFDDAF-5834-4BE3-957E-43666F824E38}"/>
+    <hyperlink ref="B2" r:id="rId24" tooltip="Go to MASTER-IT-140-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483816" xr:uid="{A854194D-A016-4B8E-9CD4-0199E9D058B1}"/>
+    <hyperlink ref="B3" r:id="rId25" tooltip="Go to MASTER-IT-145-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483817" xr:uid="{2F48F9C2-CF0F-45D1-BEAD-082AA769B618}"/>
+    <hyperlink ref="B72" r:id="rId26" tooltip="Go to MASTER-IT-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483818" xr:uid="{2641FC39-82B9-4EAD-925A-E7438719ACB9}"/>
+    <hyperlink ref="B73" r:id="rId27" tooltip="Go to MASTER-IT-202-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483819" xr:uid="{5196EE07-E0C3-4ECB-84BA-FB502943EB38}"/>
+    <hyperlink ref="B74" r:id="rId28" tooltip="Go to MASTER-IT-204-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483820" xr:uid="{B6D557EC-2AAB-48EF-AF12-71E5AC839A28}"/>
+    <hyperlink ref="B75" r:id="rId29" tooltip="Go to MASTER-IT-209-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483821" xr:uid="{B38B6B28-67D2-4AFD-9BD0-BA0AAB37775E}"/>
+    <hyperlink ref="B76" r:id="rId30" tooltip="Go to MASTER-IT-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483822" xr:uid="{9825AC83-B6B4-45CE-AADA-C61DFD06876A}"/>
+    <hyperlink ref="B77" r:id="rId31" tooltip="Go to MASTER-IT-212-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483823" xr:uid="{83F2D244-802A-4326-96EC-CC3FCA011959}"/>
+    <hyperlink ref="B78" r:id="rId32" tooltip="Go to MASTER-IT-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483824" xr:uid="{CF08E656-26BD-4FF2-A4D0-CAACB2FBC542}"/>
+    <hyperlink ref="B79" r:id="rId33" tooltip="Go to MASTER-IT-216-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483825" xr:uid="{22A443A1-9B83-479B-A3A7-2BFAC0838BC8}"/>
+    <hyperlink ref="B80" r:id="rId34" tooltip="Go to MASTER-IT-217-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483826" xr:uid="{34940FB5-197C-41D4-862F-778E2E798F4B}"/>
+    <hyperlink ref="B81" r:id="rId35" tooltip="Go to MASTER-IT-226-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483827" xr:uid="{662D5C9F-A362-4F3F-AEC4-BB2741B417C8}"/>
+    <hyperlink ref="B82" r:id="rId36" tooltip="Go to MASTER-IT-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483828" xr:uid="{1EAB80D6-2C15-4B6C-9BB7-D45BA010C0EA}"/>
+    <hyperlink ref="B83" r:id="rId37" tooltip="Go to MASTER-IT-235-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483829" xr:uid="{EB22C54A-4DB0-4B86-918F-AE5A651DE12A}"/>
+    <hyperlink ref="B84" r:id="rId38" tooltip="Go to MASTER-IT-241-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483830" xr:uid="{24F6C96F-BC9A-4427-8EB5-0A18F81286B5}"/>
+    <hyperlink ref="B85" r:id="rId39" tooltip="Go to MASTER-IT-242-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483831" xr:uid="{F07E212A-742B-45DE-ABA4-A011D8A39A9D}"/>
+    <hyperlink ref="B86" r:id="rId40" tooltip="Go to MASTER-IT-252-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483832" xr:uid="{EC042BA1-1607-4683-BDD3-23DB9EC7A0D0}"/>
+    <hyperlink ref="B87" r:id="rId41" tooltip="Go to MASTER-IT-253-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483833" xr:uid="{DA17C027-B502-49F7-A0AD-0F2F0B6C3B30}"/>
+    <hyperlink ref="B88" r:id="rId42" tooltip="Go to MASTER-IT-255-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483834" xr:uid="{977D9AD0-6044-4DF6-9016-BB6D89825017}"/>
+    <hyperlink ref="B89" r:id="rId43" tooltip="Go to MASTER-IT-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483835" xr:uid="{E4C1F23C-46B4-49F0-A494-53D7CA03C9B5}"/>
+    <hyperlink ref="B90" r:id="rId44" tooltip="Go to MASTER-IT-261-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483836" xr:uid="{D3C891B0-454D-4D17-B10E-F4DFB75E6132}"/>
+    <hyperlink ref="B91" r:id="rId45" tooltip="Go to MASTER-IT-270-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483837" xr:uid="{5B9DF672-DED3-401C-80B0-93D6A4480F37}"/>
+    <hyperlink ref="B92" r:id="rId46" tooltip="Go to MASTER-IT-272-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483838" xr:uid="{1059878A-F977-4DCB-8E3F-FE693A38811B}"/>
+    <hyperlink ref="B93" r:id="rId47" tooltip="Go to MASTER-IT-304-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483839" xr:uid="{DCE403E5-7D31-4960-8B9C-9AF327A362E0}"/>
+    <hyperlink ref="B94" r:id="rId48" tooltip="Go to MASTER-IT-312-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483840" xr:uid="{B6A81AAC-22D4-4C99-9B81-6A752FCCF21B}"/>
+    <hyperlink ref="B95" r:id="rId49" tooltip="Go to MASTER-IT-313-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483841" xr:uid="{68310F40-F60E-4098-9633-5346BC4AE60A}"/>
+    <hyperlink ref="B96" r:id="rId50" tooltip="Go to MASTER-IT-315-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483842" xr:uid="{C0E5EFAA-9AA9-4EC3-ADCE-DC53028E8B53}"/>
+    <hyperlink ref="B97" r:id="rId51" tooltip="Go to MASTER-IT-328-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483843" xr:uid="{8FAE7361-7E01-4E4E-A09F-10B386112A36}"/>
+    <hyperlink ref="B98" r:id="rId52" tooltip="Go to MASTER-IT-331-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483844" xr:uid="{5050112C-8451-4B9C-9999-6924255653A9}"/>
+    <hyperlink ref="B99" r:id="rId53" tooltip="Go to MASTER-IT-332-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483845" xr:uid="{DA86CE2B-A5DA-4671-884C-BFE0B6E153F5}"/>
+    <hyperlink ref="B100" r:id="rId54" tooltip="Go to MASTER-IT-337-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483846" xr:uid="{8653F8A8-5176-48C3-AF72-E9E303EDD79B}"/>
+    <hyperlink ref="B101" r:id="rId55" tooltip="Go to MASTER-IT-338-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483847" xr:uid="{C227140B-0AE4-4F36-B1F0-E396DCB8EE3A}"/>
+    <hyperlink ref="B102" r:id="rId56" tooltip="Go to MASTER-IT-345-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483848" xr:uid="{EFB3AD74-D60F-4BC2-A2AF-790DD022F3E4}"/>
+    <hyperlink ref="B103" r:id="rId57" tooltip="Go to MASTER-IT-355-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483849" xr:uid="{E9A0F36C-068C-4862-BEED-2B5EFB311923}"/>
+    <hyperlink ref="B104" r:id="rId58" tooltip="Go to MASTER-IT-365-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483850" xr:uid="{E0474831-7B8B-4015-B6BC-EA48A5B34269}"/>
+    <hyperlink ref="B105" r:id="rId59" tooltip="Go to MASTER-IT-390-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483851" xr:uid="{829D471E-7E49-41B7-87CA-C568DC7404A4}"/>
+    <hyperlink ref="B106" r:id="rId60" tooltip="Go to MASTER-IT-409-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483852" xr:uid="{6637F63D-A68E-4FA9-92A8-2738C4D41F3E}"/>
+    <hyperlink ref="B107" r:id="rId61" tooltip="Go to MASTER-IT-415-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483853" xr:uid="{19EEA6D4-3477-4AB0-8D6C-3708718630B9}"/>
+    <hyperlink ref="B108" r:id="rId62" tooltip="Go to MASTER-IT-420-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483854" xr:uid="{813128B3-4162-401A-89F5-EC0920E96E3F}"/>
+    <hyperlink ref="B109" r:id="rId63" tooltip="Go to MASTER-IT-423-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483855" xr:uid="{79AEDCBF-18F2-4167-B7A8-F19E11047037}"/>
+    <hyperlink ref="B110" r:id="rId64" tooltip="Go to MASTER-IT-450-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483856" xr:uid="{CCF9D67E-A8C9-4198-92EE-DDE892BF9270}"/>
+    <hyperlink ref="B111" r:id="rId65" tooltip="Go to MASTER-IT-460-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483857" xr:uid="{71506836-233F-4B1E-AC6A-D3D4CC6AEDDE}"/>
+    <hyperlink ref="B112" r:id="rId66" tooltip="Go to MASTER-IT-482-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483858" xr:uid="{8AAD6312-FFC1-4331-9CF6-FAD0E6C8468D}"/>
+    <hyperlink ref="B113" r:id="rId67" tooltip="Go to MASTER-IT-489-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483859" xr:uid="{AAA9D89A-5308-4284-BE5E-2B94302AA74B}"/>
+    <hyperlink ref="B187" r:id="rId68" tooltip="Go to MASTER-DAD-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483542" xr:uid="{B62ADAC3-689A-4F6C-BACF-DB2366E2FF6A}"/>
+    <hyperlink ref="B4" r:id="rId69" tooltip="Go to MASTER-DAD-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483543" xr:uid="{49033D59-3581-49FD-95DC-C9F09EEEE54E}"/>
+    <hyperlink ref="B55" r:id="rId70" tooltip="Go to MASTER-GAM-120-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483641" xr:uid="{0C41175B-9D42-4E45-837F-EE6B236F6EB5}"/>
+    <hyperlink ref="B56" r:id="rId71" tooltip="Go to MASTER-GAM-207-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483642" xr:uid="{91422D81-07D6-4BF5-BA43-A3F9024C4318}"/>
+    <hyperlink ref="B57" r:id="rId72" tooltip="Go to MASTER-GAM-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483643" xr:uid="{466AC651-F779-464E-9D04-5AEC01D5550F}"/>
+    <hyperlink ref="B58" r:id="rId73" tooltip="Go to MASTER-GAM-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483644" xr:uid="{6DAE3D1E-B2F1-4CA1-AF10-EE8C0D7D87E7}"/>
+    <hyperlink ref="B59" r:id="rId74" tooltip="Go to MASTER-GAM-303-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483645" xr:uid="{2E571C33-79FD-46DF-AF7C-4C039C54D697}"/>
+    <hyperlink ref="B60" r:id="rId75" tooltip="Go to MASTER-GAM-305-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483646" xr:uid="{0874430D-0CD1-4D89-9B55-BCDE4FDA02FE}"/>
+    <hyperlink ref="B61" r:id="rId76" tooltip="Go to MASTER-GAM-312-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483647" xr:uid="{C5FEE379-8AF3-4417-ADE4-57044961E383}"/>
+    <hyperlink ref="B62" r:id="rId77" tooltip="Go to MASTER-GAM-315-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2441925" xr:uid="{1A3E48FF-E145-4FDA-8922-65D7EFFD35C7}"/>
+    <hyperlink ref="B63" r:id="rId78" tooltip="Go to MASTER-GAM-325-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483648" xr:uid="{6E693B01-D331-4A28-9566-C0788E5EE1B8}"/>
+    <hyperlink ref="B64" r:id="rId79" tooltip="Go to MASTER-GAM-335-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2374297" xr:uid="{6C210166-B628-4A1E-968F-B623B7519EBB}"/>
+    <hyperlink ref="B65" r:id="rId80" tooltip="Go to MASTER-GAM-355-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2441926" xr:uid="{DC299028-DB20-497B-8D28-42C868EF139D}"/>
+    <hyperlink ref="B66" r:id="rId81" tooltip="Go to MASTER-GAM-360-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2374299" xr:uid="{376B7A00-734D-490D-B5A9-E1CC510C4514}"/>
+    <hyperlink ref="B67" r:id="rId82" tooltip="Go to MASTER-GAM-380-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483649" xr:uid="{6E9602FB-5D6F-4CF7-97C0-F0B96FFDDB21}"/>
+    <hyperlink ref="B68" r:id="rId83" tooltip="Go to MASTER-GAM-415-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483650" xr:uid="{3C4B77C6-0D84-4C23-B89E-EC49EB9B882E}"/>
+    <hyperlink ref="B69" r:id="rId84" tooltip="Go to MASTER-GAM-465-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483651" xr:uid="{FDBFACD5-4B44-43B5-AE83-34C5A73B3FA3}"/>
+    <hyperlink ref="B70" r:id="rId85" tooltip="Go to MASTER-GAM-495-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483652" xr:uid="{27A26686-8002-45A2-B8F9-437A308885CD}"/>
+    <hyperlink ref="B27" r:id="rId86" tooltip="Go to MASTER-CYB-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483529" xr:uid="{7432F9C9-3EF3-4ECB-8BB4-78C280EA7AED}"/>
+    <hyperlink ref="B28" r:id="rId87" tooltip="Go to MASTER-CYB-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483530" xr:uid="{4E09C76E-8783-44BF-AB2B-69013B0A5720}"/>
+    <hyperlink ref="B29" r:id="rId88" tooltip="Go to MASTER-CYB-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483531" xr:uid="{A5FE08F6-00C8-4BF1-9DA8-3E2A9764420F}"/>
+    <hyperlink ref="B30" r:id="rId89" tooltip="Go to MASTER-CYB-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483532" xr:uid="{5DA48EB2-CFE3-435B-BBE8-F7C4E5F206BC}"/>
+    <hyperlink ref="B31" r:id="rId90" tooltip="Go to MASTER-CYB-240-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483533" xr:uid="{1CA83868-56FA-4CC8-8832-6B6C78545ACF}"/>
+    <hyperlink ref="B32" r:id="rId91" tooltip="Go to MASTER-CYB-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483534" xr:uid="{4B485320-3C65-4E1B-AF2F-41E8E561DFF9}"/>
+    <hyperlink ref="B33" r:id="rId92" tooltip="Go to MASTER-CYB-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483535" xr:uid="{ED07A184-97BF-40EB-98CB-B39F0D4212F8}"/>
+    <hyperlink ref="B34" r:id="rId93" tooltip="Go to MASTER-CYB-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483536" xr:uid="{CC9AA3DB-1A7D-495E-B1CF-FF5D46B15720}"/>
+    <hyperlink ref="B35" r:id="rId94" tooltip="Go to MASTER-CYB-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483537" xr:uid="{1871879D-378F-4D51-936E-7FAA86BE02E1}"/>
+    <hyperlink ref="B36" r:id="rId95" tooltip="Go to MASTER-CYB-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483538" xr:uid="{16515BEA-AC8D-4D42-8D45-E2DE90BD1C55}"/>
+    <hyperlink ref="B37" r:id="rId96" tooltip="Go to MASTER-CYB-400-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483539" xr:uid="{D0CE0155-EAC7-459B-AE75-CD9B89AECA2C}"/>
+    <hyperlink ref="B38" r:id="rId97" tooltip="Go to MASTER-CYB-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483540" xr:uid="{41D2B323-290C-4373-8590-19A39A945914}"/>
+    <hyperlink ref="B39" r:id="rId98" tooltip="Go to MASTER-CYB-420-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483541" xr:uid="{64AD183A-951E-4F8B-9789-970EB8D4C72A}"/>
+    <hyperlink ref="B114" r:id="rId99" tooltip="Go to MASTER-MAT-125-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483888" xr:uid="{8CDCBF5F-0215-4432-9860-270AE868D281}"/>
+    <hyperlink ref="B115" r:id="rId100" tooltip="Go to MASTER-MAT-126-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483889" xr:uid="{FF00D006-1156-4264-9FB9-5C552B3D8AC4}"/>
+    <hyperlink ref="B116" r:id="rId101" tooltip="Go to MASTER-MAT-130-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483890" xr:uid="{70134E33-C160-4475-8707-B6552105A776}"/>
+    <hyperlink ref="B117" r:id="rId102" tooltip="Go to MASTER-MAT-133-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483891" xr:uid="{680D9F30-6AE7-4E64-9E5E-46A5F014F021}"/>
+    <hyperlink ref="B118" r:id="rId103" tooltip="Go to MASTER-MAT-135-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483892" xr:uid="{1861FE2E-5399-46EA-B6E8-67B0C3638E3F}"/>
+    <hyperlink ref="B119" r:id="rId104" tooltip="Go to MASTER-MAT-136-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483893" xr:uid="{09677CC7-A202-4DDF-8C82-8EB98D2ED8F9}"/>
+    <hyperlink ref="B120" r:id="rId105" tooltip="Go to MASTER-MAT-140-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483894" xr:uid="{EABF214B-F932-4EAB-B632-3EE7B05C4AB8}"/>
+    <hyperlink ref="B121" r:id="rId106" tooltip="Go to MASTER-MAT-142-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483895" xr:uid="{4D62A1D2-D965-4451-80EB-8CA4AE8C1CE4}"/>
+    <hyperlink ref="B122" r:id="rId107" tooltip="Go to MASTER-MAT-225-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483896" xr:uid="{1425ABA6-C70B-4549-A0F1-377A6D3DB938}"/>
+    <hyperlink ref="B123" r:id="rId108" tooltip="Go to MASTER-MAT-230-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483897" xr:uid="{BACA5C0E-A64E-4145-84C4-39145908B411}"/>
+    <hyperlink ref="B124" r:id="rId109" tooltip="Go to MASTER-MAT-240-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483898" xr:uid="{2D971353-6D36-413F-95AA-68EA08FEA80F}"/>
+    <hyperlink ref="B125" r:id="rId110" tooltip="Go to MASTER-MAT-243-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483899" xr:uid="{CD299913-81B8-4841-A16B-27D8E4405B87}"/>
+    <hyperlink ref="B126" r:id="rId111" tooltip="Go to MASTER-MAT-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483900" xr:uid="{E1954F85-F13C-42C0-9AC2-FF99791962D8}"/>
+    <hyperlink ref="B127" r:id="rId112" tooltip="Go to MASTER-MAT-275-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483901" xr:uid="{813D7C5E-B930-4589-A85B-4F65A3A63195}"/>
+    <hyperlink ref="B128" r:id="rId113" tooltip="Go to MASTER-MAT-299-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483902" xr:uid="{E5835416-A7B8-483E-BA3B-593920C5332D}"/>
+    <hyperlink ref="B129" r:id="rId114" tooltip="Go to MASTER-MAT-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483903" xr:uid="{799AFF61-62E1-40C6-878D-478876A9B3ED}"/>
+    <hyperlink ref="B130" r:id="rId115" tooltip="Go to MASTER-MAT-303-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483904" xr:uid="{456545BE-2F5A-4F7E-B309-EFC999CA35CE}"/>
+    <hyperlink ref="B131" r:id="rId116" tooltip="Go to MASTER-MAT-325-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483905" xr:uid="{BDCF02A3-467A-490C-909B-80CA5ACB89D5}"/>
+    <hyperlink ref="B132" r:id="rId117" tooltip="Go to MASTER-MAT-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483906" xr:uid="{27ECB989-62C2-4DB8-915E-0AD137B7C000}"/>
+    <hyperlink ref="B133" r:id="rId118" tooltip="Go to MASTER-MAT-350-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483907" xr:uid="{E483ABFC-2AC5-426F-B894-0AADF110AE6E}"/>
+    <hyperlink ref="B134" r:id="rId119" tooltip="Go to MASTER-MAT-375-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483908" xr:uid="{7A9E3618-A4E9-4C96-A90F-246205CE2F0E}"/>
+    <hyperlink ref="B135" r:id="rId120" tooltip="Go to MASTER-MAT-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483909" xr:uid="{BF2F601A-4761-45FF-8F81-83415FAE76B4}"/>
+    <hyperlink ref="B136" r:id="rId121" tooltip="Go to MASTER-MAT-415-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483910" xr:uid="{7166DFE2-9BB7-4931-8434-D4F679D38CDC}"/>
+    <hyperlink ref="B137" r:id="rId122" tooltip="Go to MASTER-MAT-420-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483911" xr:uid="{2DA42189-C18C-4DA6-B5B5-1D3C5AD20682}"/>
+    <hyperlink ref="B138" r:id="rId123" tooltip="Go to MASTER-MAT-430-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483912" xr:uid="{CB3152D7-6876-4CBA-B821-AE7E47AA3F24}"/>
+    <hyperlink ref="B139" r:id="rId124" tooltip="Go to MASTER-MAT-450-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483913" xr:uid="{673E9DD6-FA7C-40C8-BC67-7CA48B278F26}"/>
+    <hyperlink ref="B140" r:id="rId125" tooltip="Go to MASTER-MAT-470-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483914" xr:uid="{2BD55DEF-ACAD-4DE8-97E8-22C687F97858}"/>
+    <hyperlink ref="B163" r:id="rId126" tooltip="Go to MASTER-PHY-101-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484016" xr:uid="{8D6D42AE-CD16-428F-A13B-CF6938CEB691}"/>
+    <hyperlink ref="B164" r:id="rId127" tooltip="Go to MASTER-PHY-101L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484017" xr:uid="{9D86C117-C887-4FC8-9788-2874B7CEFC04}"/>
+    <hyperlink ref="B165" r:id="rId128" tooltip="Go to MASTER-PHY-103-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484018" xr:uid="{B3E66FA6-F823-4012-AC26-A789D411B912}"/>
+    <hyperlink ref="B166" r:id="rId129" tooltip="Go to MASTER-PHY-105-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484019" xr:uid="{2E0560AB-641E-4525-B345-A63319ED0029}"/>
+    <hyperlink ref="B167" r:id="rId130" tooltip="Go to MASTER-PHY-150-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484020" xr:uid="{9B232A33-F008-4005-9439-7575D16EB3D2}"/>
+    <hyperlink ref="B168" r:id="rId131" tooltip="Go to MASTER-PHY-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484021" xr:uid="{4B791B6D-AA47-4327-9C7D-03E08A104555}"/>
+    <hyperlink ref="B169" r:id="rId132" tooltip="Go to MASTER-PHY-205L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484022" xr:uid="{B3CB2E30-E2BC-4453-9A88-B8EBC39F040C}"/>
+    <hyperlink ref="B40" r:id="rId133" tooltip="Go to MASTER-DAT-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483544" xr:uid="{F809EB20-E9BC-49B8-B68A-BC917B695673}"/>
+    <hyperlink ref="B41" r:id="rId134" tooltip="Go to MASTER-DAT-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483545" xr:uid="{D80A8745-285B-41E3-AB02-7AB5438051A2}"/>
+    <hyperlink ref="B42" r:id="rId135" tooltip="Go to MASTER-DAT-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483546" xr:uid="{D7977F02-8867-4E9A-9A2A-7F63D958FB35}"/>
+    <hyperlink ref="B43" r:id="rId136" tooltip="Go to MASTER-DAT-223-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483547" xr:uid="{643B0DC2-BE46-452B-8E57-BEF1EDF2AD64}"/>
+    <hyperlink ref="B44" r:id="rId137" tooltip="Go to MASTER-DAT-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483548" xr:uid="{26B3BE76-983D-4383-AD0C-D6AF38484C6C}"/>
+    <hyperlink ref="B45" r:id="rId138" tooltip="Go to MASTER-DAT-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483549" xr:uid="{CE1A388F-8F09-483C-A2E2-819ADED15167}"/>
+    <hyperlink ref="B46" r:id="rId139" tooltip="Go to MASTER-DAT-300-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483550" xr:uid="{4377332A-B6CA-43A9-B420-7452BC46D0AB}"/>
+    <hyperlink ref="B47" r:id="rId140" tooltip="Go to MASTER-DAT-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483551" xr:uid="{D58509E3-4B98-4B9B-AFC3-44FA29F7FF69}"/>
+    <hyperlink ref="B48" r:id="rId141" tooltip="Go to MASTER-DAT-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483552" xr:uid="{ED590D1A-4987-4CD9-9F25-B613321B7A3A}"/>
+    <hyperlink ref="B49" r:id="rId142" tooltip="Go to MASTER-DAT-325-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483553" xr:uid="{4617C594-BA42-41EE-A398-C79EA590E630}"/>
+    <hyperlink ref="B50" r:id="rId143" tooltip="Go to MASTER-DAT-375-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483554" xr:uid="{4F94CAA0-F5FC-4FCF-B12F-C306B09C421C}"/>
+    <hyperlink ref="B51" r:id="rId144" tooltip="Go to MASTER-DAT-410-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483555" xr:uid="{946543D5-E01C-4895-AC6B-517ED1EC7BC7}"/>
+    <hyperlink ref="B52" r:id="rId145" tooltip="Go to MASTER-DAT-430-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483556" xr:uid="{5A4CC67F-A231-4681-A052-0B00ABC13BF2}"/>
+    <hyperlink ref="B53" r:id="rId146" tooltip="Go to MASTER-DAT-475-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483557" xr:uid="{B43A6170-90F4-4A6E-A3DB-85565598BF56}"/>
+    <hyperlink ref="B54" r:id="rId147" tooltip="Go to MASTER-DAT-490-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483558" xr:uid="{06A36F06-3021-40AF-94F4-24828F193F54}"/>
+    <hyperlink ref="B141" r:id="rId148" tooltip="Go to MASTER-BIO-120-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483406" xr:uid="{1A85F4C2-734F-40BD-8749-1632EC503F1B}"/>
+    <hyperlink ref="B142" r:id="rId149" tooltip="Go to MASTER-BIO-120L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483407" xr:uid="{2386945F-CE29-4F8A-A81D-DCD0AE2C1C78}"/>
+    <hyperlink ref="B143" r:id="rId150" tooltip="Go to MASTER-BIO-205-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483408" xr:uid="{2B6C8B1F-0269-45D5-A056-3FD89617E470}"/>
+    <hyperlink ref="B144" r:id="rId151" tooltip="Go to MASTER-BIO-210-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483409" xr:uid="{31CE2608-9B97-4569-BA9B-3C1787FE6309}"/>
+    <hyperlink ref="B145" r:id="rId152" tooltip="Go to MASTER-BIO-211-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483410" xr:uid="{08367A92-A988-4A9C-B4F6-B2E091A36042}"/>
+    <hyperlink ref="B146" r:id="rId153" tooltip="Go to MASTER-BIO-212-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483411" xr:uid="{04779CE1-3EBD-494D-98D4-FF56FEF17C0D}"/>
+    <hyperlink ref="B147" r:id="rId154" tooltip="Go to MASTER-BIO-315-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483412" xr:uid="{38765AC3-2133-4568-B032-1D4418C3A5BA}"/>
+    <hyperlink ref="B148" r:id="rId155" tooltip="Go to MASTER-BIO-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483413" xr:uid="{259A90C3-DF76-422A-9F70-06B9FA8E7377}"/>
+    <hyperlink ref="B149" r:id="rId156" tooltip="Go to MASTER-CHM-101-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483434" xr:uid="{1C7B820A-6F8C-49E9-8A91-B4DDBF14F236}"/>
+    <hyperlink ref="B150" r:id="rId157" tooltip="Go to MASTER-CHM-101L-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483435" xr:uid="{17B1EA1E-382A-4E89-94CC-E3E284BA5CF1}"/>
+    <hyperlink ref="B151" r:id="rId158" tooltip="Go to MASTER-ENV-101-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483589" xr:uid="{A447EB88-5A10-4AEA-B0AE-35DA169109A2}"/>
+    <hyperlink ref="B152" r:id="rId159" tooltip="Go to MASTER-ENV-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483590" xr:uid="{52CFF6AD-B69E-42A5-B758-3D35DDD50312}"/>
+    <hyperlink ref="B153" r:id="rId160" tooltip="Go to MASTER-ENV-250-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483591" xr:uid="{94A869A4-9F0C-435E-B634-4020B170B58C}"/>
+    <hyperlink ref="B154" r:id="rId161" tooltip="Go to MASTER-ENV-280-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483592" xr:uid="{BDE77CEE-8A2F-4F48-B21B-21A72C9C6144}"/>
+    <hyperlink ref="B155" r:id="rId162" tooltip="Go to MASTER-ENV-305-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483593" xr:uid="{5166CC6E-A4BA-46B9-9CF9-DBA325A5F73E}"/>
+    <hyperlink ref="B156" r:id="rId163" tooltip="Go to MASTER-ENV-319-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483594" xr:uid="{53FF6D9B-EEA2-4D30-BA16-5D120D1F2568}"/>
+    <hyperlink ref="B157" r:id="rId164" tooltip="Go to MASTER-ENV-361-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483595" xr:uid="{870C2430-8AD6-4AB5-9B28-8A405A3A7B79}"/>
+    <hyperlink ref="B158" r:id="rId165" tooltip="Go to MASTER-ENV-440-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483596" xr:uid="{BF1A9F12-D39B-4180-A75E-F8D57C4F521C}"/>
+    <hyperlink ref="B159" r:id="rId166" tooltip="Go to MASTER-GEO-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483655" xr:uid="{A0057BD4-9F6B-4790-AA97-1FA0037C8214}"/>
+    <hyperlink ref="B160" r:id="rId167" tooltip="Go to MASTER-GEO-330-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483656" xr:uid="{87BA3298-695F-4BD5-ADF4-CDDA984AB001}"/>
+    <hyperlink ref="B161" r:id="rId168" tooltip="Go to MASTER-GEO-345-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483657" xr:uid="{68AC775B-1874-4D4F-8E25-1BF024AD96CA}"/>
+    <hyperlink ref="B162" r:id="rId169" tooltip="Go to MASTER-GEO-450-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2483658" xr:uid="{299D78A2-B69B-4557-92DC-F00727430D69}"/>
+    <hyperlink ref="B170" r:id="rId170" tooltip="Go to MASTER-SCI-100-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484113" xr:uid="{095BE097-D2D1-4D58-986D-072F6A917F39}"/>
+    <hyperlink ref="B171" r:id="rId171" tooltip="Go to MASTER-SCI-200-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484114" xr:uid="{D91E72CC-7791-48AB-BC1B-6E1B17E38590}"/>
+    <hyperlink ref="B172" r:id="rId172" tooltip="Go to MASTER-SCI-207-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484115" xr:uid="{A0D561D9-184E-473F-924C-8715E771D765}"/>
+    <hyperlink ref="B173" r:id="rId173" tooltip="Go to MASTER-SCI-212-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484116" xr:uid="{2106654A-1851-4F0C-8CD4-83EFD298C15B}"/>
+    <hyperlink ref="B174" r:id="rId174" tooltip="Go to MASTER-SCI-214-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484117" xr:uid="{D140712F-6DBD-49AE-A499-2697137DAF06}"/>
+    <hyperlink ref="B175" r:id="rId175" tooltip="Go to MASTER-SCI-215-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484118" xr:uid="{B801697F-80C5-470B-9079-DFD752B4FA7C}"/>
+    <hyperlink ref="B176" r:id="rId176" tooltip="Go to MASTER-SCI-218-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484119" xr:uid="{5A00CB28-95CB-442E-8390-876BFD1F764F}"/>
+    <hyperlink ref="B177" r:id="rId177" tooltip="Go to MASTER-SCI-219-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484120" xr:uid="{48A979D8-2B84-4B85-BEA9-0A1313988436}"/>
+    <hyperlink ref="B178" r:id="rId178" tooltip="Go to MASTER-SCI-220-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484121" xr:uid="{F60AB33D-13FC-4B55-94A3-D384DCAD4045}"/>
+    <hyperlink ref="B179" r:id="rId179" tooltip="Go to MASTER-SCI-225-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484122" xr:uid="{141D2663-BEFA-47FA-837F-E0978D57B5E1}"/>
+    <hyperlink ref="B180" r:id="rId180" tooltip="Go to MASTER-SCI-260-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484123" xr:uid="{11456F76-E0BF-4B36-AC20-383D377CDD7E}"/>
+    <hyperlink ref="B181" r:id="rId181" tooltip="Go to MASTER-SCI-310-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484124" xr:uid="{4A1EC514-B6D6-492C-9BCB-2F7B2DF78843}"/>
+    <hyperlink ref="B182" r:id="rId182" tooltip="Go to MASTER-SCI-320-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484125" xr:uid="{B09612BC-C632-42C8-A891-B7F58AC7CF61}"/>
+    <hyperlink ref="B183" r:id="rId183" tooltip="Go to MASTER-SCI-333-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484126" xr:uid="{88ADFB7C-030D-46B2-9F8D-5DCC37958617}"/>
+    <hyperlink ref="B184" r:id="rId184" tooltip="Go to MASTER-SCI-350-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484127" xr:uid="{B2C2AA2C-291F-4D46-80B3-17C2A3569312}"/>
+    <hyperlink ref="B185" r:id="rId185" tooltip="Go to MASTER-SCI-425-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484128" xr:uid="{9710237F-394A-41B7-B1A5-A610CC5CBAAE}"/>
+    <hyperlink ref="B186" r:id="rId186" tooltip="Go to MASTER-SCI-489-GC-M01.202711-1 course page" display="https://learn.snhu.edu/d2l/p/home/2484129" xr:uid="{BFB4BE87-8336-4648-96AA-AF57E37E1D66}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId187"/>
